--- a/artfynd/A 8423-2023 artfynd.xlsx
+++ b/artfynd/A 8423-2023 artfynd.xlsx
@@ -880,7 +880,7 @@
         <v>131785581</v>
       </c>
       <c r="B4" t="n">
-        <v>99074</v>
+        <v>99073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8423-2023 artfynd.xlsx
+++ b/artfynd/A 8423-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131785582</v>
       </c>
       <c r="B2" t="n">
-        <v>91843</v>
+        <v>91849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131785575</v>
       </c>
       <c r="B3" t="n">
-        <v>78930</v>
+        <v>78932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131785581</v>
       </c>
       <c r="B4" t="n">
-        <v>99073</v>
+        <v>99079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>131785583</v>
       </c>
       <c r="B5" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 8423-2023 artfynd.xlsx
+++ b/artfynd/A 8423-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131785582</v>
       </c>
       <c r="B2" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131785575</v>
       </c>
       <c r="B3" t="n">
-        <v>78932</v>
+        <v>78935</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131785581</v>
       </c>
       <c r="B4" t="n">
-        <v>99079</v>
+        <v>99082</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>131785583</v>
       </c>
       <c r="B5" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 8423-2023 artfynd.xlsx
+++ b/artfynd/A 8423-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131785582</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>91857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131785575</v>
       </c>
       <c r="B3" t="n">
-        <v>78935</v>
+        <v>78940</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131785581</v>
       </c>
       <c r="B4" t="n">
-        <v>99082</v>
+        <v>99087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>131785583</v>
       </c>
       <c r="B5" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 8423-2023 artfynd.xlsx
+++ b/artfynd/A 8423-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131785582</v>
       </c>
       <c r="B2" t="n">
-        <v>91857</v>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131785575</v>
       </c>
       <c r="B3" t="n">
-        <v>78940</v>
+        <v>78942</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131785581</v>
       </c>
       <c r="B4" t="n">
-        <v>99087</v>
+        <v>99089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>131785583</v>
       </c>
       <c r="B5" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 8423-2023 artfynd.xlsx
+++ b/artfynd/A 8423-2023 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131785582</v>
+        <v>131785575</v>
       </c>
       <c r="B2" t="n">
-        <v>91903</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509979</v>
+        <v>510280</v>
       </c>
       <c r="R2" t="n">
-        <v>7012306</v>
+        <v>7012228</v>
       </c>
       <c r="S2" t="n">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131785575</v>
+        <v>131785582</v>
       </c>
       <c r="B3" t="n">
-        <v>78983</v>
+        <v>91985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,13 +811,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510280</v>
+        <v>509979</v>
       </c>
       <c r="R3" t="n">
-        <v>7012228</v>
+        <v>7012306</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131785581</v>
+        <v>131785583</v>
       </c>
       <c r="B4" t="n">
-        <v>99133</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509711</v>
+        <v>509979</v>
       </c>
       <c r="R4" t="n">
-        <v>7012332</v>
+        <v>7012306</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kalktallskog?</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,32 +983,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131785583</v>
+        <v>131785581</v>
       </c>
       <c r="B5" t="n">
-        <v>79317</v>
+        <v>99230</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509979</v>
+        <v>509711</v>
       </c>
       <c r="R5" t="n">
-        <v>7012306</v>
+        <v>7012332</v>
       </c>
       <c r="S5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Kalktallskog?</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 8423-2023 artfynd.xlsx
+++ b/artfynd/A 8423-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131785575</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131785582</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131785583</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,8 +1106,19 @@
           <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131785581</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>